--- a/Assets/Excel/EuipmentIcon.xlsx
+++ b/Assets/Excel/EuipmentIcon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenBox\Assets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\OpenBox\OpenBox\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07B36F8-E6B7-49E0-A376-1BE81D222766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839DA120-52E9-4584-88E1-C35957E4602B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="160">
   <si>
     <t>Int</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -204,62 +207,365 @@
     <t>Equip1001</t>
   </si>
   <si>
+    <t>槽位1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>槽位2</t>
+  </si>
+  <si>
+    <t>槽位3</t>
+  </si>
+  <si>
+    <t>槽位4</t>
+  </si>
+  <si>
+    <t>槽位5</t>
+  </si>
+  <si>
+    <t>槽位6</t>
+  </si>
+  <si>
+    <t>槽位7</t>
+  </si>
+  <si>
+    <t>槽位8</t>
+  </si>
+  <si>
+    <t>槽位9</t>
+  </si>
+  <si>
+    <t>槽位10</t>
+  </si>
+  <si>
+    <t>槽位11</t>
+  </si>
+  <si>
+    <t>槽位12</t>
+  </si>
+  <si>
+    <t>Equip2001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip2002</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip2003</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip2004</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip2005</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip2006</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip2007</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip2008</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip3001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip3002</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip3003</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip3004</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip3005</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip3006</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip3007</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip3008</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>Equip1002</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Equip1003</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Equip1004</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Equip1005</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Equip1006</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Equip1007</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Equip1008</t>
-  </si>
-  <si>
-    <t>槽位1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>槽位2</t>
-  </si>
-  <si>
-    <t>槽位3</t>
-  </si>
-  <si>
-    <t>槽位4</t>
-  </si>
-  <si>
-    <t>槽位5</t>
-  </si>
-  <si>
-    <t>槽位6</t>
-  </si>
-  <si>
-    <t>槽位7</t>
-  </si>
-  <si>
-    <t>槽位8</t>
-  </si>
-  <si>
-    <t>槽位9</t>
-  </si>
-  <si>
-    <t>槽位10</t>
-  </si>
-  <si>
-    <t>槽位11</t>
-  </si>
-  <si>
-    <t>槽位12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip4001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip4002</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip4003</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip4004</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip4005</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip4006</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip4007</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip4008</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip5001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip5002</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip5003</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip5004</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip5005</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip5006</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip5007</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip5008</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip6001</t>
+  </si>
+  <si>
+    <t>Equip7001</t>
+  </si>
+  <si>
+    <t>Equip8001</t>
+  </si>
+  <si>
+    <t>Equip9001</t>
+  </si>
+  <si>
+    <t>Equip10001</t>
+  </si>
+  <si>
+    <t>Equip11001</t>
+  </si>
+  <si>
+    <t>Equip12001</t>
+  </si>
+  <si>
+    <t>Equip6002</t>
+  </si>
+  <si>
+    <t>Equip7002</t>
+  </si>
+  <si>
+    <t>Equip8002</t>
+  </si>
+  <si>
+    <t>Equip9002</t>
+  </si>
+  <si>
+    <t>Equip10002</t>
+  </si>
+  <si>
+    <t>Equip11002</t>
+  </si>
+  <si>
+    <t>Equip12002</t>
+  </si>
+  <si>
+    <t>Equip6003</t>
+  </si>
+  <si>
+    <t>Equip7003</t>
+  </si>
+  <si>
+    <t>Equip8003</t>
+  </si>
+  <si>
+    <t>Equip9003</t>
+  </si>
+  <si>
+    <t>Equip10003</t>
+  </si>
+  <si>
+    <t>Equip11003</t>
+  </si>
+  <si>
+    <t>Equip12003</t>
+  </si>
+  <si>
+    <t>Equip6004</t>
+  </si>
+  <si>
+    <t>Equip7004</t>
+  </si>
+  <si>
+    <t>Equip8004</t>
+  </si>
+  <si>
+    <t>Equip9004</t>
+  </si>
+  <si>
+    <t>Equip10004</t>
+  </si>
+  <si>
+    <t>Equip11004</t>
+  </si>
+  <si>
+    <t>Equip12004</t>
+  </si>
+  <si>
+    <t>Equip6005</t>
+  </si>
+  <si>
+    <t>Equip7005</t>
+  </si>
+  <si>
+    <t>Equip8005</t>
+  </si>
+  <si>
+    <t>Equip9005</t>
+  </si>
+  <si>
+    <t>Equip10005</t>
+  </si>
+  <si>
+    <t>Equip11005</t>
+  </si>
+  <si>
+    <t>Equip12005</t>
+  </si>
+  <si>
+    <t>Equip6006</t>
+  </si>
+  <si>
+    <t>Equip7006</t>
+  </si>
+  <si>
+    <t>Equip8006</t>
+  </si>
+  <si>
+    <t>Equip9006</t>
+  </si>
+  <si>
+    <t>Equip10006</t>
+  </si>
+  <si>
+    <t>Equip11006</t>
+  </si>
+  <si>
+    <t>Equip12006</t>
+  </si>
+  <si>
+    <t>Equip6007</t>
+  </si>
+  <si>
+    <t>Equip7007</t>
+  </si>
+  <si>
+    <t>Equip8007</t>
+  </si>
+  <si>
+    <t>Equip9007</t>
+  </si>
+  <si>
+    <t>Equip10007</t>
+  </si>
+  <si>
+    <t>Equip11007</t>
+  </si>
+  <si>
+    <t>Equip12007</t>
+  </si>
+  <si>
+    <t>Equip6008</t>
+  </si>
+  <si>
+    <t>Equip7008</t>
+  </si>
+  <si>
+    <t>Equip8008</t>
+  </si>
+  <si>
+    <t>Equip9008</t>
+  </si>
+  <si>
+    <t>Equip10008</t>
+  </si>
+  <si>
+    <t>Equip11008</t>
+  </si>
+  <si>
+    <t>Equip12008</t>
   </si>
 </sst>
 </file>
@@ -869,10 +1175,10 @@
         <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="E4" s="2">
         <f>B4+10</f>
@@ -883,7 +1189,7 @@
         <v>槽位1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H4" s="2">
         <f>E4+10</f>
@@ -894,7 +1200,7 @@
         <v>槽位1</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="K4" s="2">
         <f>H4+10</f>
@@ -905,7 +1211,7 @@
         <v>槽位1</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="N4" s="2">
         <f>K4+10</f>
@@ -916,7 +1222,7 @@
         <v>槽位1</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="Q4" s="2">
         <f>N4+10</f>
@@ -927,7 +1233,7 @@
         <v>槽位1</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="T4" s="2">
         <f>Q4+10</f>
@@ -938,7 +1244,7 @@
         <v>槽位1</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="W4" s="2">
         <f>T4+10</f>
@@ -949,7 +1255,7 @@
         <v>槽位1</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.2">
@@ -960,10 +1266,10 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="E5" s="2">
         <f t="shared" ref="E5:E15" si="0">B5+10</f>
@@ -973,9 +1279,8 @@
         <f t="shared" ref="F5:F15" si="1">C5</f>
         <v>槽位2</v>
       </c>
-      <c r="G5" s="2" t="str">
-        <f>G4</f>
-        <v>Equip1002</v>
+      <c r="G5" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="H5" s="2">
         <f t="shared" ref="H5:H15" si="2">E5+10</f>
@@ -985,9 +1290,8 @@
         <f t="shared" ref="I5:I15" si="3">F5</f>
         <v>槽位2</v>
       </c>
-      <c r="J5" s="2" t="str">
-        <f>J4</f>
-        <v>Equip1003</v>
+      <c r="J5" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="K5" s="2">
         <f t="shared" ref="K5:K15" si="4">H5+10</f>
@@ -997,9 +1301,8 @@
         <f t="shared" ref="L5:L15" si="5">I5</f>
         <v>槽位2</v>
       </c>
-      <c r="M5" s="2" t="str">
-        <f>M4</f>
-        <v>Equip1004</v>
+      <c r="M5" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="N5" s="2">
         <f t="shared" ref="N5:N15" si="6">K5+10</f>
@@ -1009,9 +1312,8 @@
         <f t="shared" ref="O5:O15" si="7">L5</f>
         <v>槽位2</v>
       </c>
-      <c r="P5" s="2" t="str">
-        <f>P4</f>
-        <v>Equip1005</v>
+      <c r="P5" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="Q5" s="2">
         <f t="shared" ref="Q5:Q15" si="8">N5+10</f>
@@ -1021,9 +1323,8 @@
         <f t="shared" ref="R5:R15" si="9">O5</f>
         <v>槽位2</v>
       </c>
-      <c r="S5" s="2" t="str">
-        <f>S4</f>
-        <v>Equip1006</v>
+      <c r="S5" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="T5" s="2">
         <f t="shared" ref="T5:T15" si="10">Q5+10</f>
@@ -1033,9 +1334,8 @@
         <f t="shared" ref="U5:U15" si="11">R5</f>
         <v>槽位2</v>
       </c>
-      <c r="V5" s="2" t="str">
-        <f>V4</f>
-        <v>Equip1007</v>
+      <c r="V5" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="W5" s="2">
         <f t="shared" ref="W5:W15" si="12">T5+10</f>
@@ -1045,9 +1345,8 @@
         <f t="shared" ref="X5:X15" si="13">U5</f>
         <v>槽位2</v>
       </c>
-      <c r="Y5" s="2" t="str">
-        <f>Y4</f>
-        <v>Equip1008</v>
+      <c r="Y5" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.2">
@@ -1058,7 +1357,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>52</v>
@@ -1071,9 +1370,8 @@
         <f t="shared" si="1"/>
         <v>槽位3</v>
       </c>
-      <c r="G6" s="2" t="str">
-        <f t="shared" ref="G6:G15" si="14">G5</f>
-        <v>Equip1002</v>
+      <c r="G6" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="H6" s="2">
         <f t="shared" si="2"/>
@@ -1083,9 +1381,8 @@
         <f t="shared" si="3"/>
         <v>槽位3</v>
       </c>
-      <c r="J6" s="2" t="str">
-        <f t="shared" ref="J6:J15" si="15">J5</f>
-        <v>Equip1003</v>
+      <c r="J6" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="K6" s="2">
         <f t="shared" si="4"/>
@@ -1095,9 +1392,8 @@
         <f t="shared" si="5"/>
         <v>槽位3</v>
       </c>
-      <c r="M6" s="2" t="str">
-        <f t="shared" ref="M6:M15" si="16">M5</f>
-        <v>Equip1004</v>
+      <c r="M6" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="N6" s="2">
         <f t="shared" si="6"/>
@@ -1107,9 +1403,8 @@
         <f t="shared" si="7"/>
         <v>槽位3</v>
       </c>
-      <c r="P6" s="2" t="str">
-        <f t="shared" ref="P6:P15" si="17">P5</f>
-        <v>Equip1005</v>
+      <c r="P6" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="Q6" s="2">
         <f t="shared" si="8"/>
@@ -1119,9 +1414,8 @@
         <f t="shared" si="9"/>
         <v>槽位3</v>
       </c>
-      <c r="S6" s="2" t="str">
-        <f t="shared" ref="S6:S15" si="18">S5</f>
-        <v>Equip1006</v>
+      <c r="S6" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="T6" s="2">
         <f t="shared" si="10"/>
@@ -1131,9 +1425,8 @@
         <f t="shared" si="11"/>
         <v>槽位3</v>
       </c>
-      <c r="V6" s="2" t="str">
-        <f t="shared" ref="V6:V15" si="19">V5</f>
-        <v>Equip1007</v>
+      <c r="V6" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="W6" s="2">
         <f t="shared" si="12"/>
@@ -1143,9 +1436,8 @@
         <f t="shared" si="13"/>
         <v>槽位3</v>
       </c>
-      <c r="Y6" s="2" t="str">
-        <f t="shared" ref="Y6:Y15" si="20">Y5</f>
-        <v>Equip1008</v>
+      <c r="Y6" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.2">
@@ -1156,10 +1448,10 @@
         <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="E7" s="2">
         <f t="shared" si="0"/>
@@ -1169,9 +1461,8 @@
         <f t="shared" si="1"/>
         <v>槽位4</v>
       </c>
-      <c r="G7" s="2" t="str">
-        <f t="shared" si="14"/>
-        <v>Equip1002</v>
+      <c r="G7" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="H7" s="2">
         <f t="shared" si="2"/>
@@ -1181,9 +1472,8 @@
         <f t="shared" si="3"/>
         <v>槽位4</v>
       </c>
-      <c r="J7" s="2" t="str">
-        <f t="shared" si="15"/>
-        <v>Equip1003</v>
+      <c r="J7" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="K7" s="2">
         <f t="shared" si="4"/>
@@ -1193,9 +1483,8 @@
         <f t="shared" si="5"/>
         <v>槽位4</v>
       </c>
-      <c r="M7" s="2" t="str">
-        <f t="shared" si="16"/>
-        <v>Equip1004</v>
+      <c r="M7" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="N7" s="2">
         <f t="shared" si="6"/>
@@ -1205,9 +1494,8 @@
         <f t="shared" si="7"/>
         <v>槽位4</v>
       </c>
-      <c r="P7" s="2" t="str">
-        <f t="shared" si="17"/>
-        <v>Equip1005</v>
+      <c r="P7" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="Q7" s="2">
         <f t="shared" si="8"/>
@@ -1217,9 +1505,8 @@
         <f t="shared" si="9"/>
         <v>槽位4</v>
       </c>
-      <c r="S7" s="2" t="str">
-        <f t="shared" si="18"/>
-        <v>Equip1006</v>
+      <c r="S7" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="T7" s="2">
         <f t="shared" si="10"/>
@@ -1229,9 +1516,8 @@
         <f t="shared" si="11"/>
         <v>槽位4</v>
       </c>
-      <c r="V7" s="2" t="str">
-        <f t="shared" si="19"/>
-        <v>Equip1007</v>
+      <c r="V7" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="W7" s="2">
         <f t="shared" si="12"/>
@@ -1241,9 +1527,8 @@
         <f t="shared" si="13"/>
         <v>槽位4</v>
       </c>
-      <c r="Y7" s="2" t="str">
-        <f t="shared" si="20"/>
-        <v>Equip1008</v>
+      <c r="Y7" s="2" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.2">
@@ -1254,10 +1539,10 @@
         <v>9</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="E8" s="2">
         <f t="shared" si="0"/>
@@ -1267,9 +1552,8 @@
         <f t="shared" si="1"/>
         <v>槽位5</v>
       </c>
-      <c r="G8" s="2" t="str">
-        <f t="shared" si="14"/>
-        <v>Equip1002</v>
+      <c r="G8" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="H8" s="2">
         <f t="shared" si="2"/>
@@ -1279,9 +1563,8 @@
         <f t="shared" si="3"/>
         <v>槽位5</v>
       </c>
-      <c r="J8" s="2" t="str">
-        <f t="shared" si="15"/>
-        <v>Equip1003</v>
+      <c r="J8" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="K8" s="2">
         <f t="shared" si="4"/>
@@ -1291,9 +1574,8 @@
         <f t="shared" si="5"/>
         <v>槽位5</v>
       </c>
-      <c r="M8" s="2" t="str">
-        <f t="shared" si="16"/>
-        <v>Equip1004</v>
+      <c r="M8" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="N8" s="2">
         <f t="shared" si="6"/>
@@ -1303,9 +1585,8 @@
         <f t="shared" si="7"/>
         <v>槽位5</v>
       </c>
-      <c r="P8" s="2" t="str">
-        <f t="shared" si="17"/>
-        <v>Equip1005</v>
+      <c r="P8" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="Q8" s="2">
         <f t="shared" si="8"/>
@@ -1315,9 +1596,8 @@
         <f t="shared" si="9"/>
         <v>槽位5</v>
       </c>
-      <c r="S8" s="2" t="str">
-        <f t="shared" si="18"/>
-        <v>Equip1006</v>
+      <c r="S8" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="T8" s="2">
         <f t="shared" si="10"/>
@@ -1327,9 +1607,8 @@
         <f t="shared" si="11"/>
         <v>槽位5</v>
       </c>
-      <c r="V8" s="2" t="str">
-        <f t="shared" si="19"/>
-        <v>Equip1007</v>
+      <c r="V8" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="W8" s="2">
         <f t="shared" si="12"/>
@@ -1339,9 +1618,8 @@
         <f t="shared" si="13"/>
         <v>槽位5</v>
       </c>
-      <c r="Y8" s="2" t="str">
-        <f t="shared" si="20"/>
-        <v>Equip1008</v>
+      <c r="Y8" s="2" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.2">
@@ -1352,10 +1630,10 @@
         <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="E9" s="2">
         <f t="shared" si="0"/>
@@ -1365,9 +1643,8 @@
         <f t="shared" si="1"/>
         <v>槽位6</v>
       </c>
-      <c r="G9" s="2" t="str">
-        <f t="shared" si="14"/>
-        <v>Equip1002</v>
+      <c r="G9" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="H9" s="2">
         <f t="shared" si="2"/>
@@ -1377,9 +1654,8 @@
         <f t="shared" si="3"/>
         <v>槽位6</v>
       </c>
-      <c r="J9" s="2" t="str">
-        <f t="shared" si="15"/>
-        <v>Equip1003</v>
+      <c r="J9" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="K9" s="2">
         <f t="shared" si="4"/>
@@ -1389,9 +1665,8 @@
         <f t="shared" si="5"/>
         <v>槽位6</v>
       </c>
-      <c r="M9" s="2" t="str">
-        <f t="shared" si="16"/>
-        <v>Equip1004</v>
+      <c r="M9" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="N9" s="2">
         <f t="shared" si="6"/>
@@ -1401,9 +1676,8 @@
         <f t="shared" si="7"/>
         <v>槽位6</v>
       </c>
-      <c r="P9" s="2" t="str">
-        <f t="shared" si="17"/>
-        <v>Equip1005</v>
+      <c r="P9" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="Q9" s="2">
         <f t="shared" si="8"/>
@@ -1413,9 +1687,8 @@
         <f t="shared" si="9"/>
         <v>槽位6</v>
       </c>
-      <c r="S9" s="2" t="str">
-        <f t="shared" si="18"/>
-        <v>Equip1006</v>
+      <c r="S9" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="T9" s="2">
         <f t="shared" si="10"/>
@@ -1425,9 +1698,8 @@
         <f t="shared" si="11"/>
         <v>槽位6</v>
       </c>
-      <c r="V9" s="2" t="str">
-        <f t="shared" si="19"/>
-        <v>Equip1007</v>
+      <c r="V9" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="W9" s="2">
         <f t="shared" si="12"/>
@@ -1437,9 +1709,8 @@
         <f t="shared" si="13"/>
         <v>槽位6</v>
       </c>
-      <c r="Y9" s="2" t="str">
-        <f t="shared" si="20"/>
-        <v>Equip1008</v>
+      <c r="Y9" s="2" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.2">
@@ -1450,10 +1721,10 @@
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="E10" s="2">
         <f t="shared" si="0"/>
@@ -1463,9 +1734,8 @@
         <f t="shared" si="1"/>
         <v>槽位7</v>
       </c>
-      <c r="G10" s="2" t="str">
-        <f t="shared" si="14"/>
-        <v>Equip1002</v>
+      <c r="G10" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="H10" s="2">
         <f t="shared" si="2"/>
@@ -1475,9 +1745,8 @@
         <f t="shared" si="3"/>
         <v>槽位7</v>
       </c>
-      <c r="J10" s="2" t="str">
-        <f t="shared" si="15"/>
-        <v>Equip1003</v>
+      <c r="J10" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="K10" s="2">
         <f t="shared" si="4"/>
@@ -1487,9 +1756,8 @@
         <f t="shared" si="5"/>
         <v>槽位7</v>
       </c>
-      <c r="M10" s="2" t="str">
-        <f t="shared" si="16"/>
-        <v>Equip1004</v>
+      <c r="M10" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="N10" s="2">
         <f t="shared" si="6"/>
@@ -1499,9 +1767,8 @@
         <f t="shared" si="7"/>
         <v>槽位7</v>
       </c>
-      <c r="P10" s="2" t="str">
-        <f t="shared" si="17"/>
-        <v>Equip1005</v>
+      <c r="P10" s="2" t="s">
+        <v>133</v>
       </c>
       <c r="Q10" s="2">
         <f t="shared" si="8"/>
@@ -1511,9 +1778,8 @@
         <f t="shared" si="9"/>
         <v>槽位7</v>
       </c>
-      <c r="S10" s="2" t="str">
-        <f t="shared" si="18"/>
-        <v>Equip1006</v>
+      <c r="S10" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="T10" s="2">
         <f t="shared" si="10"/>
@@ -1523,9 +1789,8 @@
         <f t="shared" si="11"/>
         <v>槽位7</v>
       </c>
-      <c r="V10" s="2" t="str">
-        <f t="shared" si="19"/>
-        <v>Equip1007</v>
+      <c r="V10" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="W10" s="2">
         <f t="shared" si="12"/>
@@ -1535,9 +1800,8 @@
         <f t="shared" si="13"/>
         <v>槽位7</v>
       </c>
-      <c r="Y10" s="2" t="str">
-        <f t="shared" si="20"/>
-        <v>Equip1008</v>
+      <c r="Y10" s="2" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.2">
@@ -1548,10 +1812,10 @@
         <v>9</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="E11" s="2">
         <f t="shared" si="0"/>
@@ -1561,9 +1825,8 @@
         <f t="shared" si="1"/>
         <v>槽位8</v>
       </c>
-      <c r="G11" s="2" t="str">
-        <f t="shared" si="14"/>
-        <v>Equip1002</v>
+      <c r="G11" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="H11" s="2">
         <f t="shared" si="2"/>
@@ -1573,9 +1836,8 @@
         <f t="shared" si="3"/>
         <v>槽位8</v>
       </c>
-      <c r="J11" s="2" t="str">
-        <f t="shared" si="15"/>
-        <v>Equip1003</v>
+      <c r="J11" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="K11" s="2">
         <f t="shared" si="4"/>
@@ -1585,9 +1847,8 @@
         <f t="shared" si="5"/>
         <v>槽位8</v>
       </c>
-      <c r="M11" s="2" t="str">
-        <f t="shared" si="16"/>
-        <v>Equip1004</v>
+      <c r="M11" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="N11" s="2">
         <f t="shared" si="6"/>
@@ -1597,9 +1858,8 @@
         <f t="shared" si="7"/>
         <v>槽位8</v>
       </c>
-      <c r="P11" s="2" t="str">
-        <f t="shared" si="17"/>
-        <v>Equip1005</v>
+      <c r="P11" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="Q11" s="2">
         <f t="shared" si="8"/>
@@ -1609,9 +1869,8 @@
         <f t="shared" si="9"/>
         <v>槽位8</v>
       </c>
-      <c r="S11" s="2" t="str">
-        <f t="shared" si="18"/>
-        <v>Equip1006</v>
+      <c r="S11" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="T11" s="2">
         <f t="shared" si="10"/>
@@ -1621,9 +1880,8 @@
         <f t="shared" si="11"/>
         <v>槽位8</v>
       </c>
-      <c r="V11" s="2" t="str">
-        <f t="shared" si="19"/>
-        <v>Equip1007</v>
+      <c r="V11" s="2" t="s">
+        <v>148</v>
       </c>
       <c r="W11" s="2">
         <f t="shared" si="12"/>
@@ -1633,9 +1891,8 @@
         <f t="shared" si="13"/>
         <v>槽位8</v>
       </c>
-      <c r="Y11" s="2" t="str">
-        <f t="shared" si="20"/>
-        <v>Equip1008</v>
+      <c r="Y11" s="2" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.2">
@@ -1646,10 +1903,10 @@
         <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="E12" s="2">
         <f t="shared" si="0"/>
@@ -1659,9 +1916,8 @@
         <f t="shared" si="1"/>
         <v>槽位9</v>
       </c>
-      <c r="G12" s="2" t="str">
-        <f t="shared" si="14"/>
-        <v>Equip1002</v>
+      <c r="G12" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="H12" s="2">
         <f t="shared" si="2"/>
@@ -1671,9 +1927,8 @@
         <f t="shared" si="3"/>
         <v>槽位9</v>
       </c>
-      <c r="J12" s="2" t="str">
-        <f t="shared" si="15"/>
-        <v>Equip1003</v>
+      <c r="J12" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="K12" s="2">
         <f t="shared" si="4"/>
@@ -1683,9 +1938,8 @@
         <f t="shared" si="5"/>
         <v>槽位9</v>
       </c>
-      <c r="M12" s="2" t="str">
-        <f t="shared" si="16"/>
-        <v>Equip1004</v>
+      <c r="M12" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="N12" s="2">
         <f t="shared" si="6"/>
@@ -1695,9 +1949,8 @@
         <f t="shared" si="7"/>
         <v>槽位9</v>
       </c>
-      <c r="P12" s="2" t="str">
-        <f t="shared" si="17"/>
-        <v>Equip1005</v>
+      <c r="P12" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="Q12" s="2">
         <f t="shared" si="8"/>
@@ -1707,9 +1960,8 @@
         <f t="shared" si="9"/>
         <v>槽位9</v>
       </c>
-      <c r="S12" s="2" t="str">
-        <f t="shared" si="18"/>
-        <v>Equip1006</v>
+      <c r="S12" s="2" t="s">
+        <v>142</v>
       </c>
       <c r="T12" s="2">
         <f t="shared" si="10"/>
@@ -1719,9 +1971,8 @@
         <f t="shared" si="11"/>
         <v>槽位9</v>
       </c>
-      <c r="V12" s="2" t="str">
-        <f t="shared" si="19"/>
-        <v>Equip1007</v>
+      <c r="V12" s="2" t="s">
+        <v>149</v>
       </c>
       <c r="W12" s="2">
         <f t="shared" si="12"/>
@@ -1731,9 +1982,8 @@
         <f t="shared" si="13"/>
         <v>槽位9</v>
       </c>
-      <c r="Y12" s="2" t="str">
-        <f t="shared" si="20"/>
-        <v>Equip1008</v>
+      <c r="Y12" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.2">
@@ -1744,10 +1994,10 @@
         <v>9</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>52</v>
+        <v>108</v>
       </c>
       <c r="E13" s="2">
         <f t="shared" si="0"/>
@@ -1757,9 +2007,8 @@
         <f t="shared" si="1"/>
         <v>槽位10</v>
       </c>
-      <c r="G13" s="2" t="str">
-        <f t="shared" si="14"/>
-        <v>Equip1002</v>
+      <c r="G13" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="H13" s="2">
         <f t="shared" si="2"/>
@@ -1769,9 +2018,8 @@
         <f t="shared" si="3"/>
         <v>槽位10</v>
       </c>
-      <c r="J13" s="2" t="str">
-        <f t="shared" si="15"/>
-        <v>Equip1003</v>
+      <c r="J13" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="K13" s="2">
         <f t="shared" si="4"/>
@@ -1781,9 +2029,8 @@
         <f t="shared" si="5"/>
         <v>槽位10</v>
       </c>
-      <c r="M13" s="2" t="str">
-        <f t="shared" si="16"/>
-        <v>Equip1004</v>
+      <c r="M13" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="N13" s="2">
         <f t="shared" si="6"/>
@@ -1793,9 +2040,8 @@
         <f t="shared" si="7"/>
         <v>槽位10</v>
       </c>
-      <c r="P13" s="2" t="str">
-        <f t="shared" si="17"/>
-        <v>Equip1005</v>
+      <c r="P13" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="Q13" s="2">
         <f t="shared" si="8"/>
@@ -1805,9 +2051,8 @@
         <f t="shared" si="9"/>
         <v>槽位10</v>
       </c>
-      <c r="S13" s="2" t="str">
-        <f t="shared" si="18"/>
-        <v>Equip1006</v>
+      <c r="S13" s="2" t="s">
+        <v>143</v>
       </c>
       <c r="T13" s="2">
         <f t="shared" si="10"/>
@@ -1817,9 +2062,8 @@
         <f t="shared" si="11"/>
         <v>槽位10</v>
       </c>
-      <c r="V13" s="2" t="str">
-        <f t="shared" si="19"/>
-        <v>Equip1007</v>
+      <c r="V13" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="W13" s="2">
         <f t="shared" si="12"/>
@@ -1829,9 +2073,8 @@
         <f t="shared" si="13"/>
         <v>槽位10</v>
       </c>
-      <c r="Y13" s="2" t="str">
-        <f t="shared" si="20"/>
-        <v>Equip1008</v>
+      <c r="Y13" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.2">
@@ -1842,10 +2085,10 @@
         <v>9</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="E14" s="2">
         <f t="shared" si="0"/>
@@ -1855,9 +2098,8 @@
         <f t="shared" si="1"/>
         <v>槽位11</v>
       </c>
-      <c r="G14" s="2" t="str">
-        <f t="shared" si="14"/>
-        <v>Equip1002</v>
+      <c r="G14" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="H14" s="2">
         <f t="shared" si="2"/>
@@ -1867,9 +2109,8 @@
         <f t="shared" si="3"/>
         <v>槽位11</v>
       </c>
-      <c r="J14" s="2" t="str">
-        <f t="shared" si="15"/>
-        <v>Equip1003</v>
+      <c r="J14" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="K14" s="2">
         <f t="shared" si="4"/>
@@ -1879,9 +2120,8 @@
         <f t="shared" si="5"/>
         <v>槽位11</v>
       </c>
-      <c r="M14" s="2" t="str">
-        <f t="shared" si="16"/>
-        <v>Equip1004</v>
+      <c r="M14" s="2" t="s">
+        <v>130</v>
       </c>
       <c r="N14" s="2">
         <f t="shared" si="6"/>
@@ -1891,9 +2131,8 @@
         <f t="shared" si="7"/>
         <v>槽位11</v>
       </c>
-      <c r="P14" s="2" t="str">
-        <f t="shared" si="17"/>
-        <v>Equip1005</v>
+      <c r="P14" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="Q14" s="2">
         <f t="shared" si="8"/>
@@ -1903,9 +2142,8 @@
         <f t="shared" si="9"/>
         <v>槽位11</v>
       </c>
-      <c r="S14" s="2" t="str">
-        <f t="shared" si="18"/>
-        <v>Equip1006</v>
+      <c r="S14" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="T14" s="2">
         <f t="shared" si="10"/>
@@ -1915,9 +2153,8 @@
         <f t="shared" si="11"/>
         <v>槽位11</v>
       </c>
-      <c r="V14" s="2" t="str">
-        <f t="shared" si="19"/>
-        <v>Equip1007</v>
+      <c r="V14" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="W14" s="2">
         <f t="shared" si="12"/>
@@ -1927,9 +2164,8 @@
         <f t="shared" si="13"/>
         <v>槽位11</v>
       </c>
-      <c r="Y14" s="2" t="str">
-        <f t="shared" si="20"/>
-        <v>Equip1008</v>
+      <c r="Y14" s="2" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.2">
@@ -1940,10 +2176,10 @@
         <v>9</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="E15" s="2">
         <f t="shared" si="0"/>
@@ -1953,9 +2189,8 @@
         <f t="shared" si="1"/>
         <v>槽位12</v>
       </c>
-      <c r="G15" s="2" t="str">
-        <f t="shared" si="14"/>
-        <v>Equip1002</v>
+      <c r="G15" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="H15" s="2">
         <f t="shared" si="2"/>
@@ -1965,9 +2200,8 @@
         <f t="shared" si="3"/>
         <v>槽位12</v>
       </c>
-      <c r="J15" s="2" t="str">
-        <f t="shared" si="15"/>
-        <v>Equip1003</v>
+      <c r="J15" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="K15" s="2">
         <f t="shared" si="4"/>
@@ -1977,9 +2211,8 @@
         <f t="shared" si="5"/>
         <v>槽位12</v>
       </c>
-      <c r="M15" s="2" t="str">
-        <f t="shared" si="16"/>
-        <v>Equip1004</v>
+      <c r="M15" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="N15" s="2">
         <f t="shared" si="6"/>
@@ -1989,9 +2222,8 @@
         <f t="shared" si="7"/>
         <v>槽位12</v>
       </c>
-      <c r="P15" s="2" t="str">
-        <f t="shared" si="17"/>
-        <v>Equip1005</v>
+      <c r="P15" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="Q15" s="2">
         <f t="shared" si="8"/>
@@ -2001,9 +2233,8 @@
         <f t="shared" si="9"/>
         <v>槽位12</v>
       </c>
-      <c r="S15" s="2" t="str">
-        <f t="shared" si="18"/>
-        <v>Equip1006</v>
+      <c r="S15" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="T15" s="2">
         <f t="shared" si="10"/>
@@ -2013,9 +2244,8 @@
         <f t="shared" si="11"/>
         <v>槽位12</v>
       </c>
-      <c r="V15" s="2" t="str">
-        <f t="shared" si="19"/>
-        <v>Equip1007</v>
+      <c r="V15" s="2" t="s">
+        <v>152</v>
       </c>
       <c r="W15" s="2">
         <f t="shared" si="12"/>
@@ -2025,13 +2255,13 @@
         <f t="shared" si="13"/>
         <v>槽位12</v>
       </c>
-      <c r="Y15" s="2" t="str">
-        <f t="shared" si="20"/>
-        <v>Equip1008</v>
+      <c r="Y15" s="2" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>